--- a/reports/一级子公司B_资产负债表_2026-12.xlsx
+++ b/reports/一级子公司B_资产负债表_2026-12.xlsx
@@ -2691,10 +2691,10 @@
         </is>
       </c>
       <c r="F5" s="16" t="n">
-        <v>0</v>
+        <v>1809710</v>
       </c>
       <c r="G5" s="16" t="n">
-        <v>0</v>
+        <v>1889337</v>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1">
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="F6" s="16" t="n">
-        <v>0</v>
+        <v>1932280</v>
       </c>
       <c r="G6" s="16" t="n">
-        <v>0</v>
+        <v>2017300</v>
       </c>
     </row>
     <row r="7" ht="16.5" customHeight="1">
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0</v>
+        <v>2177420</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0</v>
+        <v>2273226</v>
       </c>
     </row>
     <row r="9" ht="16.5" customHeight="1">
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="F14" s="16" t="n">
-        <v>0</v>
+        <v>2912840</v>
       </c>
       <c r="G14" s="16" t="n">
-        <v>0</v>
+        <v>3041005</v>
       </c>
     </row>
     <row r="15" ht="16.5" customHeight="1">
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="F15" s="16" t="n">
-        <v>0</v>
+        <v>3035410</v>
       </c>
       <c r="G15" s="16" t="n">
-        <v>0</v>
+        <v>3168968</v>
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1">
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="F16" s="16" t="n">
-        <v>0</v>
+        <v>3157980</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>0</v>
+        <v>3296931</v>
       </c>
     </row>
     <row r="17" ht="16.5" customHeight="1">
@@ -3219,10 +3219,10 @@
         </is>
       </c>
       <c r="F21" s="16" t="n">
-        <v>0</v>
+        <v>3770830</v>
       </c>
       <c r="G21" s="16" t="n">
-        <v>0</v>
+        <v>3936747</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1">
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="F29" s="19" t="n">
-        <v>243736500</v>
+        <v>262532970</v>
       </c>
       <c r="G29" s="19" t="n"/>
     </row>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="F31" s="16" t="n">
-        <v>0</v>
+        <v>4996530</v>
       </c>
       <c r="G31" s="16" t="n">
-        <v>0</v>
+        <v>5216377</v>
       </c>
     </row>
     <row r="32" ht="16.5" customHeight="1">
@@ -4325,7 +4325,7 @@
         </is>
       </c>
       <c r="F55" s="19" t="n">
-        <v>471600000</v>
+        <v>476596530</v>
       </c>
       <c r="G55" s="19" t="n"/>
     </row>
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="F56" s="19" t="n">
-        <v>715336500</v>
+        <v>739129500</v>
       </c>
       <c r="G56" s="19" t="n"/>
     </row>
@@ -4478,10 +4478,10 @@
         </is>
       </c>
       <c r="F60" s="16" t="n">
-        <v>0</v>
+        <v>8551060</v>
       </c>
       <c r="G60" s="16" t="n">
-        <v>0</v>
+        <v>8927307</v>
       </c>
     </row>
     <row r="61" ht="16.5" customHeight="1">
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="F62" s="16" t="n">
-        <v>0</v>
+        <v>8796200</v>
       </c>
       <c r="G62" s="16" t="n">
-        <v>0</v>
+        <v>9183233</v>
       </c>
     </row>
     <row r="63" ht="16.5" customHeight="1">
@@ -4742,10 +4742,10 @@
         </is>
       </c>
       <c r="F68" s="16" t="n">
-        <v>0</v>
+        <v>9531620</v>
       </c>
       <c r="G68" s="16" t="n">
-        <v>0</v>
+        <v>9951011</v>
       </c>
     </row>
     <row r="69" ht="16.5" customHeight="1">
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="F69" s="16" t="n">
-        <v>0</v>
+        <v>9654190</v>
       </c>
       <c r="G69" s="16" t="n">
-        <v>0</v>
+        <v>10078974</v>
       </c>
     </row>
     <row r="70" ht="16.5" customHeight="1">
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="F70" s="16" t="n">
-        <v>0</v>
+        <v>9776760</v>
       </c>
       <c r="G70" s="16" t="n">
-        <v>0</v>
+        <v>10206937</v>
       </c>
     </row>
     <row r="71" ht="16.5" customHeight="1">
@@ -5072,10 +5072,10 @@
         </is>
       </c>
       <c r="F78" s="16" t="n">
-        <v>0</v>
+        <v>10757320</v>
       </c>
       <c r="G78" s="16" t="n">
-        <v>0</v>
+        <v>11230642</v>
       </c>
     </row>
     <row r="79" ht="16.5" customHeight="1">
@@ -5105,10 +5105,10 @@
         </is>
       </c>
       <c r="F79" s="16" t="n">
-        <v>0</v>
+        <v>10879890</v>
       </c>
       <c r="G79" s="16" t="n">
-        <v>0</v>
+        <v>11358605</v>
       </c>
     </row>
     <row r="80" ht="16.5" customHeight="1">
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="F84" s="19" t="n">
-        <v>116182000</v>
+        <v>184129040</v>
       </c>
       <c r="G84" s="19" t="n"/>
     </row>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="F86" s="16" t="n">
-        <v>0</v>
+        <v>11737880</v>
       </c>
       <c r="G86" s="16" t="n">
-        <v>0</v>
+        <v>12254347</v>
       </c>
     </row>
     <row r="87" ht="16.5" customHeight="1">
@@ -5718,7 +5718,7 @@
         </is>
       </c>
       <c r="F98" s="19" t="n">
-        <v>154000000</v>
+        <v>165737880</v>
       </c>
       <c r="G98" s="19" t="n"/>
     </row>
@@ -5749,7 +5749,7 @@
         </is>
       </c>
       <c r="F99" s="19" t="n">
-        <v>270182000</v>
+        <v>349866920</v>
       </c>
       <c r="G99" s="19" t="n"/>
     </row>
@@ -6467,7 +6467,7 @@
         </is>
       </c>
       <c r="F121" s="16" t="n">
-        <v>100154500</v>
+        <v>44262580</v>
       </c>
       <c r="G121" s="16" t="n">
         <v>124273816</v>
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="F122" s="19" t="n">
-        <v>445154500</v>
+        <v>389262580</v>
       </c>
       <c r="G122" s="19" t="n"/>
     </row>
@@ -6564,7 +6564,7 @@
         </is>
       </c>
       <c r="F124" s="19" t="n">
-        <v>445154500</v>
+        <v>389262580</v>
       </c>
       <c r="G124" s="19" t="n"/>
     </row>
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="F125" s="25" t="n">
-        <v>715336500</v>
+        <v>739129500</v>
       </c>
       <c r="G125" s="25" t="n"/>
     </row>
